--- a/research/traditional_assets/database/data/denmark/denmark_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_electronics_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.9370370370370371</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="H2">
-        <v>-1.029292929292929</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="I2">
-        <v>-1.097466118826407</v>
+        <v>-0.05534591194968554</v>
       </c>
       <c r="J2">
-        <v>-1.097466118826407</v>
+        <v>-0.05534591194968554</v>
       </c>
       <c r="K2">
-        <v>-2.464</v>
+        <v>-0.521</v>
       </c>
       <c r="L2">
-        <v>-0.8296296296296297</v>
+        <v>-0.1092243186582809</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.81</v>
+        <v>1.38</v>
       </c>
       <c r="V2">
-        <v>0.1050218340611354</v>
-      </c>
-      <c r="W2">
-        <v>-0.3479854232449501</v>
+        <v>0.0896103896103896</v>
       </c>
       <c r="X2">
-        <v>0.06798311314195507</v>
-      </c>
-      <c r="Y2">
-        <v>-0.4159685363869051</v>
-      </c>
-      <c r="Z2">
-        <v>0.9059374966261211</v>
-      </c>
-      <c r="AA2">
-        <v>-1.06816389319001</v>
+        <v>0.1159451045873834</v>
       </c>
       <c r="AB2">
-        <v>0.06752798942522077</v>
-      </c>
-      <c r="AC2">
-        <v>-1.135691882615231</v>
+        <v>0.1152021953514747</v>
       </c>
       <c r="AD2">
-        <v>0.445</v>
+        <v>0.165</v>
       </c>
       <c r="AE2">
-        <v>0.08737186457214734</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.5323718645721474</v>
+        <v>0.165</v>
       </c>
       <c r="AG2">
-        <v>-4.277628135427853</v>
+        <v>-1.215</v>
       </c>
       <c r="AH2">
-        <v>0.01149027867876592</v>
+        <v>0.01060070671378092</v>
       </c>
       <c r="AI2">
-        <v>0.05376205537956231</v>
+        <v>0.05564924114671164</v>
       </c>
       <c r="AJ2">
-        <v>-0.1030198407109211</v>
+        <v>-0.08565385971096227</v>
       </c>
       <c r="AK2">
-        <v>-0.8400070240721222</v>
+        <v>-0.7665615141955835</v>
       </c>
       <c r="AL2">
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="AM2">
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="AN2">
-        <v>-0.1435483870967742</v>
+        <v>-0.6653225806451614</v>
       </c>
       <c r="AO2">
-        <v>-52.3015873015873</v>
+        <v>-88</v>
       </c>
       <c r="AP2">
-        <v>1.379880043686404</v>
+        <v>4.899193548387096</v>
       </c>
       <c r="AQ2">
-        <v>-52.3015873015873</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +689,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realfiction Holding AB (publ) (OM:REALFI)</t>
+          <t>Q-Interline A/S (CPSE:QINTER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +698,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.4255102040816326</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="H3">
-        <v>-0.5035714285714286</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="I3">
-        <v>-0.2933673469387755</v>
+        <v>-0.05534591194968554</v>
       </c>
       <c r="J3">
-        <v>-0.2933673469387755</v>
+        <v>-0.05534591194968554</v>
       </c>
       <c r="K3">
-        <v>-0.314</v>
+        <v>-0.521</v>
       </c>
       <c r="L3">
-        <v>-0.1602040816326531</v>
+        <v>-0.1092243186582809</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,198 +737,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.31</v>
+        <v>1.38</v>
       </c>
       <c r="V3">
-        <v>0.104746835443038</v>
-      </c>
-      <c r="W3">
-        <v>-0.1286885245901639</v>
+        <v>0.0896103896103896</v>
       </c>
       <c r="X3">
-        <v>0.06814537044105604</v>
-      </c>
-      <c r="Y3">
-        <v>-0.19683389503122</v>
-      </c>
-      <c r="Z3">
-        <v>1.088284286507496</v>
-      </c>
-      <c r="AA3">
-        <v>-0.3192670738478623</v>
+        <v>0.1159451045873834</v>
       </c>
       <c r="AB3">
-        <v>0.06750195000953318</v>
-      </c>
-      <c r="AC3">
-        <v>-0.3867690238573955</v>
+        <v>0.1152021953514747</v>
       </c>
       <c r="AD3">
-        <v>0.445</v>
+        <v>0.165</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.445</v>
+        <v>0.165</v>
       </c>
       <c r="AG3">
-        <v>-2.865</v>
+        <v>-1.215</v>
       </c>
       <c r="AH3">
-        <v>0.0138867217974723</v>
+        <v>0.01060070671378092</v>
       </c>
       <c r="AI3">
-        <v>0.06587712805329386</v>
+        <v>0.05564924114671164</v>
       </c>
       <c r="AJ3">
-        <v>-0.09970419349225684</v>
+        <v>-0.08565385971096227</v>
       </c>
       <c r="AK3">
-        <v>-0.8316400580551526</v>
+        <v>-0.7665615141955835</v>
       </c>
       <c r="AL3">
-        <v>0.044</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>0.044</v>
+        <v>0.003</v>
       </c>
       <c r="AN3">
-        <v>-0.9408033826638479</v>
+        <v>-0.6653225806451614</v>
       </c>
       <c r="AO3">
-        <v>-13.06818181818182</v>
+        <v>-88</v>
       </c>
       <c r="AP3">
-        <v>6.05708245243129</v>
+        <v>4.899193548387096</v>
       </c>
       <c r="AQ3">
-        <v>-13.06818181818182</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Shape Robotics A/S (CPSE:SHAPE)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Electronics (General)</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-1.92970297029703</v>
-      </c>
-      <c r="H4">
-        <v>-2.04950495049505</v>
-      </c>
-      <c r="I4">
-        <v>-2.657895418727158</v>
-      </c>
-      <c r="J4">
-        <v>-2.657895418727158</v>
-      </c>
-      <c r="K4">
-        <v>-2.15</v>
-      </c>
-      <c r="L4">
-        <v>-2.128712871287129</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1.5</v>
-      </c>
-      <c r="V4">
-        <v>0.1056338028169014</v>
-      </c>
-      <c r="W4">
-        <v>-0.5672823218997362</v>
-      </c>
-      <c r="X4">
-        <v>0.06782085584285412</v>
-      </c>
-      <c r="Y4">
-        <v>-0.6351031777425903</v>
-      </c>
-      <c r="Z4">
-        <v>0.683646429325023</v>
-      </c>
-      <c r="AA4">
-        <v>-1.817060712532159</v>
-      </c>
-      <c r="AB4">
-        <v>0.06755402884090836</v>
-      </c>
-      <c r="AC4">
-        <v>-1.884614741373067</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0.08737186457214734</v>
-      </c>
-      <c r="AF4">
-        <v>0.08737186457214734</v>
-      </c>
-      <c r="AG4">
-        <v>-1.412628135427853</v>
-      </c>
-      <c r="AH4">
-        <v>0.006115320956179494</v>
-      </c>
-      <c r="AI4">
-        <v>0.02776026104688606</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1104705603613192</v>
-      </c>
-      <c r="AK4">
-        <v>-0.8575041044510846</v>
-      </c>
-      <c r="AL4">
-        <v>0.019</v>
-      </c>
-      <c r="AM4">
-        <v>0.019</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AO4">
-        <v>-143.1578947368421</v>
-      </c>
-      <c r="AP4">
-        <v>0.5377343492302447</v>
-      </c>
-      <c r="AQ4">
-        <v>-143.1578947368421</v>
+        <v>-88</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_electronics_general.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.01886792452830189</v>
+        <v>-0.3648192771084337</v>
       </c>
       <c r="H2">
-        <v>0.01886792452830189</v>
+        <v>-0.4072289156626506</v>
       </c>
       <c r="I2">
-        <v>-0.05534591194968554</v>
+        <v>-0.4120481927710843</v>
       </c>
       <c r="J2">
-        <v>-0.05534591194968554</v>
+        <v>-0.4120481927710843</v>
       </c>
       <c r="K2">
-        <v>-0.521</v>
+        <v>-1.74</v>
       </c>
       <c r="L2">
-        <v>-0.1092243186582809</v>
+        <v>-0.4192771084337349</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.38</v>
+        <v>0.105</v>
       </c>
       <c r="V2">
-        <v>0.0896103896103896</v>
+        <v>0.006402439024390244</v>
+      </c>
+      <c r="W2">
+        <v>-0.6214285714285714</v>
       </c>
       <c r="X2">
-        <v>0.1159451045873834</v>
+        <v>0.1007381005021436</v>
+      </c>
+      <c r="Y2">
+        <v>-0.722166671930715</v>
+      </c>
+      <c r="Z2">
+        <v>3.132075471698113</v>
+      </c>
+      <c r="AA2">
+        <v>-1.290566037735849</v>
       </c>
       <c r="AB2">
-        <v>0.1152021953514747</v>
+        <v>0.09687269950057861</v>
+      </c>
+      <c r="AC2">
+        <v>-1.387438737236428</v>
       </c>
       <c r="AD2">
-        <v>0.165</v>
+        <v>1.15</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.165</v>
+        <v>1.15</v>
       </c>
       <c r="AG2">
-        <v>-1.215</v>
+        <v>1.045</v>
       </c>
       <c r="AH2">
-        <v>0.01060070671378092</v>
+        <v>0.06552706552706554</v>
       </c>
       <c r="AI2">
-        <v>0.05564924114671164</v>
+        <v>0.4872881355932203</v>
       </c>
       <c r="AJ2">
-        <v>-0.08565385971096227</v>
+        <v>0.05990255087417597</v>
       </c>
       <c r="AK2">
-        <v>-0.7665615141955835</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="AL2">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="AM2">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="AN2">
-        <v>-0.6653225806451614</v>
+        <v>-0.680473372781065</v>
       </c>
       <c r="AO2">
-        <v>-88</v>
+        <v>-142.5</v>
       </c>
       <c r="AP2">
-        <v>4.899193548387096</v>
+        <v>-0.6183431952662721</v>
       </c>
       <c r="AQ2">
-        <v>-88</v>
+        <v>-142.5</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.01886792452830189</v>
+        <v>-0.3648192771084337</v>
       </c>
       <c r="H3">
-        <v>0.01886792452830189</v>
+        <v>-0.4072289156626506</v>
       </c>
       <c r="I3">
-        <v>-0.05534591194968554</v>
+        <v>-0.4120481927710843</v>
       </c>
       <c r="J3">
-        <v>-0.05534591194968554</v>
+        <v>-0.4120481927710843</v>
       </c>
       <c r="K3">
-        <v>-0.521</v>
+        <v>-1.74</v>
       </c>
       <c r="L3">
-        <v>-0.1092243186582809</v>
+        <v>-0.4192771084337349</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.38</v>
+        <v>0.105</v>
       </c>
       <c r="V3">
-        <v>0.0896103896103896</v>
+        <v>0.006402439024390244</v>
+      </c>
+      <c r="W3">
+        <v>-0.6214285714285714</v>
       </c>
       <c r="X3">
-        <v>0.1159451045873834</v>
+        <v>0.1007381005021436</v>
+      </c>
+      <c r="Y3">
+        <v>-0.722166671930715</v>
+      </c>
+      <c r="Z3">
+        <v>3.132075471698113</v>
+      </c>
+      <c r="AA3">
+        <v>-1.290566037735849</v>
       </c>
       <c r="AB3">
-        <v>0.1152021953514747</v>
+        <v>0.09687269950057861</v>
+      </c>
+      <c r="AC3">
+        <v>-1.387438737236428</v>
       </c>
       <c r="AD3">
-        <v>0.165</v>
+        <v>1.15</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.165</v>
+        <v>1.15</v>
       </c>
       <c r="AG3">
-        <v>-1.215</v>
+        <v>1.045</v>
       </c>
       <c r="AH3">
-        <v>0.01060070671378092</v>
+        <v>0.06552706552706554</v>
       </c>
       <c r="AI3">
-        <v>0.05564924114671164</v>
+        <v>0.4872881355932203</v>
       </c>
       <c r="AJ3">
-        <v>-0.08565385971096227</v>
+        <v>0.05990255087417597</v>
       </c>
       <c r="AK3">
-        <v>-0.7665615141955835</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="AN3">
-        <v>-0.6653225806451614</v>
+        <v>-0.680473372781065</v>
       </c>
       <c r="AO3">
-        <v>-88</v>
+        <v>-142.5</v>
       </c>
       <c r="AP3">
-        <v>4.899193548387096</v>
+        <v>-0.6183431952662721</v>
       </c>
       <c r="AQ3">
-        <v>-88</v>
+        <v>-142.5</v>
       </c>
     </row>
   </sheetData>
